--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_movinterna_a_2021_arica_y_parinacota.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_movinterna_a_2021_arica_y_parinacota.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:22</t>
+    <t xml:space="preserve">2026-09-24 01:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -717,10 +717,10 @@
         <v>11</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>-0.19</v>
+        <v>-0.7</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="15">
@@ -731,10 +731,10 @@
         <v>11</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>0</v>
+        <v>-0.46</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="16">
@@ -745,10 +745,10 @@
         <v>11</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>0.01</v>
+        <v>-0.24</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="17">
@@ -759,10 +759,10 @@
         <v>11</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>0.05</v>
+        <v>0.72</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="18">
@@ -815,10 +815,10 @@
         <v>28</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>-0.21</v>
+        <v>-0.29</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="22">
@@ -829,10 +829,10 @@
         <v>28</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>-0.05</v>
+        <v>-0.17</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="23">
@@ -843,10 +843,10 @@
         <v>28</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>-0.19</v>
+        <v>-0.22</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="24">
@@ -857,10 +857,10 @@
         <v>28</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>-0.11</v>
+        <v>-0.12</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="25">
@@ -871,10 +871,10 @@
         <v>28</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>0.33</v>
+        <v>0.35</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="26">
@@ -885,10 +885,10 @@
         <v>28</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>-0.05</v>
+        <v>-0.06</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_movinterna_a_2021_arica_y_parinacota.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_movinterna_a_2021_arica_y_parinacota.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:12</t>
+    <t xml:space="preserve">2026-10-01 23:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -144,7 +144,7 @@
     <t xml:space="preserve">plot_regional_correl_matriz_m_movinterna_a_2021_arica_y_parinacota.png</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Unidad territorial</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_movinterna_a_2021_arica_y_parinacota.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_movinterna_a_2021_arica_y_parinacota.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:07</t>
+    <t xml:space="preserve">2026-10-05 19:45</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
